--- a/artfynd/A 49188-2024 artfynd.xlsx
+++ b/artfynd/A 49188-2024 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>83239138</v>
+        <v>83239136</v>
       </c>
       <c r="B2" t="n">
-        <v>100514</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223246</v>
+        <v>220785</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545974.6992195667</v>
+        <v>545952</v>
       </c>
       <c r="R2" t="n">
-        <v>6484003.432935116</v>
+        <v>6484010</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -749,7 +744,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>7D6215A7-7D16-4ACE-AA67-8AF8F199DE21</t>
+          <t>A3CA27F8-669B-4619-970F-ADDFCB361F0C</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -757,19 +752,9 @@
           <t>2001-03-12</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2001-03-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,15 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>83239151</v>
+        <v>83239142</v>
       </c>
       <c r="B3" t="n">
-        <v>103812</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -844,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546022.4706079657</v>
+        <v>545988</v>
       </c>
       <c r="R3" t="n">
-        <v>6483949.105934074</v>
+        <v>6483991</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -874,7 +854,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>75BE7C0B-EAAB-430E-B4F8-34BEFD80682D</t>
+          <t>5B4DD753-4274-4CD0-A85E-2573C77F8858</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -882,19 +862,9 @@
           <t>2001-03-12</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2001-03-12</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,15 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>83239171</v>
+        <v>83239151</v>
       </c>
       <c r="B4" t="n">
-        <v>103812</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546075.700192509</v>
+        <v>546022</v>
       </c>
       <c r="R4" t="n">
-        <v>6484098.71160455</v>
+        <v>6483949</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -999,7 +964,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>35E503F4-1E80-4C1E-9CE6-440E70811141</t>
+          <t>75BE7C0B-EAAB-430E-B4F8-34BEFD80682D</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1007,19 +972,9 @@
           <t>2001-03-12</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2001-03-12</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,15 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>83239136</v>
+        <v>83239171</v>
       </c>
       <c r="B5" t="n">
-        <v>103812</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545951.5798377357</v>
+        <v>546076</v>
       </c>
       <c r="R5" t="n">
-        <v>6484009.957252026</v>
+        <v>6484099</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1124,7 +1074,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>A3CA27F8-669B-4619-970F-ADDFCB361F0C</t>
+          <t>35E503F4-1E80-4C1E-9CE6-440E70811141</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1132,19 +1082,9 @@
           <t>2001-03-12</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2001-03-12</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1175,19 +1115,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>83239163</v>
+        <v>83239131</v>
       </c>
       <c r="B6" t="n">
-        <v>100514</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103403</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1219,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>546069.142977624</v>
+        <v>545928</v>
       </c>
       <c r="R6" t="n">
-        <v>6483988.33760875</v>
+        <v>6484037</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1249,7 +1184,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>1A05F481-0CE3-4D4B-A1C4-F460B90C0049</t>
+          <t>0DD9C652-B0AF-4CFE-BCF3-3326BA64DC13</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1257,19 +1192,9 @@
           <t>2001-03-12</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2001-03-12</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1300,15 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>83239142</v>
+        <v>83239138</v>
       </c>
       <c r="B7" t="n">
-        <v>103812</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103403</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1316,21 +1236,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220785</v>
+        <v>223246</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1344,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545987.94334924</v>
+        <v>545975</v>
       </c>
       <c r="R7" t="n">
-        <v>6483990.519907212</v>
+        <v>6484003</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1374,7 +1294,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>5B4DD753-4274-4CD0-A85E-2573C77F8858</t>
+          <t>7D6215A7-7D16-4ACE-AA67-8AF8F199DE21</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1382,19 +1302,9 @@
           <t>2001-03-12</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2001-03-12</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1425,19 +1335,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>83239131</v>
+        <v>83239147</v>
       </c>
       <c r="B8" t="n">
-        <v>100514</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103403</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1469,10 +1374,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545927.6979050594</v>
+        <v>546002</v>
       </c>
       <c r="R8" t="n">
-        <v>6484036.859442943</v>
+        <v>6483949</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1499,7 +1404,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>0DD9C652-B0AF-4CFE-BCF3-3326BA64DC13</t>
+          <t>21AA2A5C-A2EA-4E2E-BE69-E795020E68A0</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1507,19 +1412,9 @@
           <t>2001-03-12</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2001-03-12</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1550,19 +1445,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>83239147</v>
+        <v>83239158</v>
       </c>
       <c r="B9" t="n">
-        <v>100514</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103403</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1594,10 +1484,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>546001.5251589953</v>
+        <v>546022</v>
       </c>
       <c r="R9" t="n">
-        <v>6483948.859903616</v>
+        <v>6483980</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1624,7 +1514,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>21AA2A5C-A2EA-4E2E-BE69-E795020E68A0</t>
+          <t>4DD1BCD2-0F62-485E-930E-C8EC90009EFE</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1632,19 +1522,9 @@
           <t>2001-03-12</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2001-03-12</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1675,19 +1555,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>83239168</v>
+        <v>83239163</v>
       </c>
       <c r="B10" t="n">
-        <v>100514</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103403</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1719,10 +1594,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>546066.6796447237</v>
+        <v>546069</v>
       </c>
       <c r="R10" t="n">
-        <v>6484019.672990952</v>
+        <v>6483988</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1749,7 +1624,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>039DD517-754E-470F-A381-66DBAE67887A</t>
+          <t>1A05F481-0CE3-4D4B-A1C4-F460B90C0049</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1757,19 +1632,9 @@
           <t>2001-03-12</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2001-03-12</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1800,19 +1665,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>83239158</v>
+        <v>83239168</v>
       </c>
       <c r="B11" t="n">
-        <v>100514</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103403</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1844,10 +1704,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>546022.1082981803</v>
+        <v>546067</v>
       </c>
       <c r="R11" t="n">
-        <v>6483979.943590526</v>
+        <v>6484020</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1874,7 +1734,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>4DD1BCD2-0F62-485E-930E-C8EC90009EFE</t>
+          <t>039DD517-754E-470F-A381-66DBAE67887A</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1882,19 +1742,9 @@
           <t>2001-03-12</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2001-03-12</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 49188-2024 artfynd.xlsx
+++ b/artfynd/A 49188-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83239136</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83239142</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83239151</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1112,6 +1132,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83239171</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1222,6 +1247,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83239131</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1332,6 +1362,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83239138</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1442,6 +1477,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83239147</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1552,6 +1592,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83239158</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1662,6 +1707,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83239163</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1772,8 +1822,25 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83239168</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>